--- a/artfynd/A 19030-2025 artfynd.xlsx
+++ b/artfynd/A 19030-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>111525189</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405279.7231805852</v>
+        <v>405279</v>
       </c>
       <c r="R2" t="n">
-        <v>6707428.035680772</v>
+        <v>6707428</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111525190</v>
+        <v>112552417</v>
       </c>
       <c r="B3" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Nordost Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405242.5508286526</v>
+        <v>405263</v>
       </c>
       <c r="R3" t="n">
-        <v>6707460.562775456</v>
+        <v>6707465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111525191</v>
+        <v>111525190</v>
       </c>
       <c r="B4" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405242.5508286526</v>
+        <v>405242</v>
       </c>
       <c r="R4" t="n">
-        <v>6707460.562775456</v>
+        <v>6707460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112552417</v>
+        <v>111525191</v>
       </c>
       <c r="B5" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nordost Skarptjärnen, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405263</v>
+        <v>405242</v>
       </c>
       <c r="R5" t="n">
-        <v>6707464</v>
+        <v>6707460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 19030-2025 artfynd.xlsx
+++ b/artfynd/A 19030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525190</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>